--- a/CartRules_1125.xlsx
+++ b/CartRules_1125.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
   <si>
     <t>Product ID</t>
   </si>
@@ -23,6 +23,81 @@
   </si>
   <si>
     <t>Cart Rules</t>
+  </si>
+  <si>
+    <t>2423</t>
+  </si>
+  <si>
+    <t>434</t>
+  </si>
+  <si>
+    <t>2308</t>
+  </si>
+  <si>
+    <t>1446</t>
+  </si>
+  <si>
+    <t>589</t>
+  </si>
+  <si>
+    <t>1413</t>
+  </si>
+  <si>
+    <t>3429</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>8938</t>
+  </si>
+  <si>
+    <t>11690</t>
+  </si>
+  <si>
+    <t>12791</t>
+  </si>
+  <si>
+    <t>2743</t>
+  </si>
+  <si>
+    <t>947</t>
+  </si>
+  <si>
+    <t>11164</t>
+  </si>
+  <si>
+    <t>21068</t>
+  </si>
+  <si>
+    <t>9920</t>
+  </si>
+  <si>
+    <t>9921</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
 </sst>
 </file>
@@ -380,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -395,300 +470,190 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2">
-        <v>151</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>39</v>
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3">
-        <v>362</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>165</v>
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4">
-        <v>420</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>258</v>
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5">
-        <v>963</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>477</v>
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6">
-        <v>1124</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>221</v>
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7">
-        <v>2104</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>400</v>
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8">
-        <v>2105</v>
-      </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-      <c r="C8">
-        <v>350</v>
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9">
-        <v>2438</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>761</v>
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10">
-        <v>2821</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>1565</v>
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11">
-        <v>3934</v>
-      </c>
-      <c r="B11">
-        <v>5</v>
-      </c>
-      <c r="C11">
-        <v>710</v>
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12">
-        <v>4175</v>
-      </c>
-      <c r="B12">
-        <v>3</v>
-      </c>
-      <c r="C12">
-        <v>1913</v>
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13">
-        <v>4176</v>
-      </c>
-      <c r="B13">
-        <v>4</v>
-      </c>
-      <c r="C13">
-        <v>569</v>
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14">
-        <v>5733</v>
-      </c>
-      <c r="B14">
-        <v>2</v>
-      </c>
-      <c r="C14">
-        <v>59</v>
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15">
-        <v>5736</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>59</v>
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16">
-        <v>6935</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
-      </c>
-      <c r="C16">
-        <v>23</v>
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17">
-        <v>7558</v>
-      </c>
-      <c r="B17">
-        <v>3</v>
-      </c>
-      <c r="C17">
-        <v>48</v>
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18">
-        <v>8659</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19">
-        <v>8672</v>
-      </c>
-      <c r="B19">
-        <v>2</v>
-      </c>
-      <c r="C19">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20">
-        <v>10721</v>
-      </c>
-      <c r="B20">
-        <v>29</v>
-      </c>
-      <c r="C20">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21">
-        <v>11625</v>
-      </c>
-      <c r="B21">
-        <v>29</v>
-      </c>
-      <c r="C21">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22">
-        <v>12614</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23">
-        <v>12721</v>
-      </c>
-      <c r="B23">
-        <v>2</v>
-      </c>
-      <c r="C23">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24">
-        <v>13034</v>
-      </c>
-      <c r="B24">
-        <v>3</v>
-      </c>
-      <c r="C24">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25">
-        <v>13928</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26">
-        <v>21010</v>
-      </c>
-      <c r="B26">
-        <v>2</v>
-      </c>
-      <c r="C26">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27">
-        <v>21752</v>
-      </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-      <c r="C27">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28">
-        <v>24725</v>
-      </c>
-      <c r="B28">
-        <v>2</v>
-      </c>
-      <c r="C28">
-        <v>76</v>
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
